--- a/exports_hebdomadaires/export_2026-03-09.xlsx
+++ b/exports_hebdomadaires/export_2026-03-09.xlsx
@@ -1360,6 +1360,11 @@
           <t>EMY-500218</t>
         </is>
       </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE8" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -2183,6 +2188,11 @@
           <t>EMY-500237</t>
         </is>
       </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE15" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -3151,6 +3161,11 @@
           <t>EMY-500597</t>
         </is>
       </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE23" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -6782,6 +6797,11 @@
           <t>EMY-500634</t>
         </is>
       </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE53" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -7501,6 +7521,11 @@
           <t>EMY-500776</t>
         </is>
       </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE59" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -8332,6 +8357,11 @@
           <t>EMY-500796</t>
         </is>
       </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE66" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -18429,6 +18459,11 @@
           <t>EMY-500354</t>
         </is>
       </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE151" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -31232,6 +31267,11 @@
           <t>EMY-500060</t>
         </is>
       </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE259" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -32273,6 +32313,11 @@
           <t>EMY-500120</t>
         </is>
       </c>
+      <c r="AD268" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE268" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -33425,6 +33470,11 @@
           <t>EMY-500831</t>
         </is>
       </c>
+      <c r="AD278" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE278" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -36410,6 +36460,11 @@
           <t>EMY-500476</t>
         </is>
       </c>
+      <c r="AD303" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE303" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -38813,6 +38868,11 @@
           <t>EMY-500776</t>
         </is>
       </c>
+      <c r="AD323" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE323" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -42369,6 +42429,11 @@
           <t>EMY-500755</t>
         </is>
       </c>
+      <c r="AD353" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE353" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -49963,6 +50028,11 @@
           <t>EMY-500420</t>
         </is>
       </c>
+      <c r="AD418" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE418" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -50533,6 +50603,11 @@
           <t>EMY-500060</t>
         </is>
       </c>
+      <c r="AD423" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE423" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -51869,6 +51944,11 @@
           <t>EMY-500120</t>
         </is>
       </c>
+      <c r="AD434" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE434" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -57920,6 +58000,11 @@
           <t>EMY-500420</t>
         </is>
       </c>
+      <c r="AD484" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE484" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -58632,6 +58717,11 @@
           <t>EMY-500825</t>
         </is>
       </c>
+      <c r="AD490" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE490" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -63379,6 +63469,11 @@
           <t>EMY-500776</t>
         </is>
       </c>
+      <c r="AD531" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE531" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -69793,6 +69888,11 @@
           <t>EMY-500420</t>
         </is>
       </c>
+      <c r="AD585" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE585" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -73017,6 +73117,11 @@
           <t>EMY-500177</t>
         </is>
       </c>
+      <c r="AD612" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE612" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -74468,6 +74573,11 @@
           <t>EMY-500420</t>
         </is>
       </c>
+      <c r="AD624" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE624" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -80222,6 +80332,11 @@
           <t>EMY-500354</t>
         </is>
       </c>
+      <c r="AD671" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE671" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -91969,6 +92084,11 @@
           <t>EMY-500173</t>
         </is>
       </c>
+      <c r="AD771" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE771" t="inlineStr">
         <is>
           <t>Amine absent cette semaine (congés).</t>
@@ -93437,6 +93557,11 @@
       <c r="AC784" t="inlineStr">
         <is>
           <t>EMY-500060</t>
+        </is>
+      </c>
+      <c r="AD784" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
         </is>
       </c>
       <c r="AE784" t="inlineStr">

--- a/exports_hebdomadaires/export_2026-03-09.xlsx
+++ b/exports_hebdomadaires/export_2026-03-09.xlsx
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG8" t="n">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG15" t="n">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG18" t="n">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG19" t="n">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG21" t="n">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG23" t="n">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG26" t="n">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG28" t="n">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG29" t="n">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG33" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG37" t="n">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG38" t="n">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG41" t="n">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG42" t="n">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG45" t="n">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG47" t="n">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG51" t="n">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG56" t="n">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG60" t="n">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG64" t="n">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG65" t="n">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG66" t="n">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG68" t="n">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG70" t="n">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG72" t="n">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG76" t="n">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG79" t="n">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG85" t="n">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG86" t="n">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="AF90" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG90" t="n">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG91" t="n">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="AF93" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG93" t="n">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG94" t="n">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG98" t="n">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG99" t="n">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="AF103" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG103" t="n">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="AF105" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG105" t="n">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="AF106" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG106" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="AF111" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG111" t="n">
@@ -12632,7 +12632,7 @@
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG112" t="n">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="AF120" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG120" t="n">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="AF124" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG124" t="n">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG131" t="n">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG132" t="n">
@@ -14960,7 +14960,7 @@
       </c>
       <c r="AF133" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG133" t="n">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="AF134" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG134" t="n">
@@ -15194,7 +15194,7 @@
       </c>
       <c r="AF135" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG135" t="n">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="AF138" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG138" t="n">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="AF140" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG140" t="n">
@@ -15817,7 +15817,7 @@
       </c>
       <c r="AF141" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG141" t="n">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG143" t="n">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="AF144" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG144" t="n">
@@ -16376,7 +16376,7 @@
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG146" t="n">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="AF148" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG148" t="n">
@@ -16693,7 +16693,7 @@
       </c>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG149" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="AF151" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG151" t="n">
@@ -17215,7 +17215,7 @@
       </c>
       <c r="AF154" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG154" t="n">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="AF155" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG155" t="n">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="AF159" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG159" t="n">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="AF161" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG161" t="n">
@@ -18450,7 +18450,7 @@
       </c>
       <c r="AF165" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG165" t="n">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="AF167" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG167" t="n">
@@ -18787,7 +18787,7 @@
       </c>
       <c r="AF168" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG168" t="n">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="AF170" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG170" t="n">
@@ -19086,7 +19086,7 @@
       </c>
       <c r="AF171" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG171" t="n">
@@ -19317,7 +19317,7 @@
       </c>
       <c r="AF173" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG173" t="n">
@@ -19421,7 +19421,7 @@
       </c>
       <c r="AF174" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG174" t="n">
@@ -19753,7 +19753,7 @@
       </c>
       <c r="AF177" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG177" t="n">
@@ -20762,7 +20762,7 @@
       </c>
       <c r="AF186" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG186" t="n">
@@ -20985,7 +20985,7 @@
       </c>
       <c r="AF188" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG188" t="n">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="AF189" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG189" t="n">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="AF190" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG190" t="n">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="AF191" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG191" t="n">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="AF197" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG197" t="n">
@@ -22505,7 +22505,7 @@
       </c>
       <c r="AF202" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG202" t="n">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="AF204" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG204" t="n">
@@ -22959,7 +22959,7 @@
       </c>
       <c r="AF206" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG206" t="n">
@@ -23076,7 +23076,7 @@
       </c>
       <c r="AF207" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG207" t="n">
@@ -23517,7 +23517,7 @@
       </c>
       <c r="AF211" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG211" t="n">
@@ -23626,7 +23626,7 @@
       </c>
       <c r="AF212" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG212" t="n">
@@ -23968,7 +23968,7 @@
       </c>
       <c r="AF215" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG215" t="n">
@@ -24194,7 +24194,7 @@
       </c>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG217" t="n">
@@ -24645,7 +24645,7 @@
       </c>
       <c r="AF221" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG221" t="n">
@@ -24985,7 +24985,7 @@
       </c>
       <c r="AF224" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG224" t="n">
@@ -25646,7 +25646,7 @@
       </c>
       <c r="AF230" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG230" t="n">
@@ -25877,7 +25877,7 @@
       </c>
       <c r="AF232" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG232" t="n">
@@ -25981,7 +25981,7 @@
       </c>
       <c r="AF233" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG233" t="n">
@@ -26098,7 +26098,7 @@
       </c>
       <c r="AF234" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG234" t="n">
@@ -26321,7 +26321,7 @@
       </c>
       <c r="AF236" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG236" t="n">
@@ -26770,7 +26770,7 @@
       </c>
       <c r="AF240" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG240" t="n">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="AF241" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG241" t="n">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="AF242" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG242" t="n">
@@ -27772,7 +27772,7 @@
       </c>
       <c r="AF249" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG249" t="n">
@@ -27889,7 +27889,7 @@
       </c>
       <c r="AF250" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG250" t="n">
@@ -28553,7 +28553,7 @@
       </c>
       <c r="AF256" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG256" t="n">
@@ -28657,7 +28657,7 @@
       </c>
       <c r="AF257" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG257" t="n">
@@ -30318,7 +30318,7 @@
       </c>
       <c r="AF272" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG272" t="n">
@@ -30754,7 +30754,7 @@
       </c>
       <c r="AF276" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG276" t="n">
@@ -30977,7 +30977,7 @@
       </c>
       <c r="AF278" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG278" t="n">
@@ -31327,7 +31327,7 @@
       </c>
       <c r="AF281" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG281" t="n">
@@ -32079,7 +32079,7 @@
       </c>
       <c r="AF288" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG288" t="n">
@@ -32305,7 +32305,7 @@
       </c>
       <c r="AF290" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG290" t="n">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="AF295" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG295" t="n">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="AF300" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG300" t="n">
@@ -33639,7 +33639,7 @@
       </c>
       <c r="AF302" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG302" t="n">
@@ -33756,7 +33756,7 @@
       </c>
       <c r="AF303" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG303" t="n">
@@ -33956,7 +33956,7 @@
       </c>
       <c r="AF305" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG305" t="n">
@@ -34366,7 +34366,7 @@
       </c>
       <c r="AF309" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG309" t="n">
@@ -35345,7 +35345,7 @@
       </c>
       <c r="AF318" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG318" t="n">
@@ -36070,7 +36070,7 @@
       </c>
       <c r="AF325" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG325" t="n">
@@ -36182,7 +36182,7 @@
       </c>
       <c r="AF326" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG326" t="n">
@@ -36398,7 +36398,7 @@
       </c>
       <c r="AF328" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG328" t="n">
@@ -36946,7 +36946,7 @@
       </c>
       <c r="AF333" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG333" t="n">
@@ -37182,7 +37182,7 @@
       </c>
       <c r="AF335" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG335" t="n">
@@ -37286,7 +37286,7 @@
       </c>
       <c r="AF336" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG336" t="n">
@@ -37686,7 +37686,7 @@
       </c>
       <c r="AF340" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG340" t="n">
@@ -37795,7 +37795,7 @@
       </c>
       <c r="AF341" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG341" t="n">
@@ -38034,7 +38034,7 @@
       </c>
       <c r="AF343" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG343" t="n">
@@ -38366,7 +38366,7 @@
       </c>
       <c r="AF346" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG346" t="n">
@@ -38478,7 +38478,7 @@
       </c>
       <c r="AF347" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG347" t="n">
@@ -38678,7 +38678,7 @@
       </c>
       <c r="AF349" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG349" t="n">
@@ -39137,7 +39137,7 @@
       </c>
       <c r="AF353" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG353" t="n">
@@ -39246,7 +39246,7 @@
       </c>
       <c r="AF354" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG354" t="n">
@@ -39664,7 +39664,7 @@
       </c>
       <c r="AF358" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG358" t="n">
@@ -39768,7 +39768,7 @@
       </c>
       <c r="AF359" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG359" t="n">
@@ -40354,7 +40354,7 @@
       </c>
       <c r="AF364" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG364" t="n">
@@ -40997,7 +40997,7 @@
       </c>
       <c r="AF370" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG370" t="n">
@@ -41101,7 +41101,7 @@
       </c>
       <c r="AF371" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG371" t="n">
@@ -42327,7 +42327,7 @@
       </c>
       <c r="AF382" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG382" t="n">
@@ -42669,7 +42669,7 @@
       </c>
       <c r="AF385" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG385" t="n">
@@ -42781,7 +42781,7 @@
       </c>
       <c r="AF386" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG386" t="n">
@@ -43417,7 +43417,7 @@
       </c>
       <c r="AF392" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG392" t="n">
@@ -44063,7 +44063,7 @@
       </c>
       <c r="AF398" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG398" t="n">
@@ -45158,7 +45158,7 @@
       </c>
       <c r="AF408" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG408" t="n">
@@ -45682,7 +45682,7 @@
       </c>
       <c r="AF413" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG413" t="n">
@@ -46898,7 +46898,7 @@
       </c>
       <c r="AF424" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG424" t="n">
@@ -47134,7 +47134,7 @@
       </c>
       <c r="AF426" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG426" t="n">
@@ -47238,7 +47238,7 @@
       </c>
       <c r="AF427" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG427" t="n">
@@ -47674,7 +47674,7 @@
       </c>
       <c r="AF431" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG431" t="n">
@@ -47778,7 +47778,7 @@
       </c>
       <c r="AF432" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG432" t="n">
@@ -49289,7 +49289,7 @@
       </c>
       <c r="AF446" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG446" t="n">
@@ -49393,7 +49393,7 @@
       </c>
       <c r="AF447" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG447" t="n">
@@ -49710,7 +49710,7 @@
       </c>
       <c r="AF450" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG450" t="n">
@@ -49819,7 +49819,7 @@
       </c>
       <c r="AF451" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG451" t="n">
@@ -49936,7 +49936,7 @@
       </c>
       <c r="AF452" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG452" t="n">
@@ -50136,7 +50136,7 @@
       </c>
       <c r="AF454" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG454" t="n">
@@ -50240,7 +50240,7 @@
       </c>
       <c r="AF455" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG455" t="n">
@@ -50559,7 +50559,7 @@
       </c>
       <c r="AF458" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG458" t="n">
@@ -50671,7 +50671,7 @@
       </c>
       <c r="AF459" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG459" t="n">
@@ -51426,7 +51426,7 @@
       </c>
       <c r="AF466" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG466" t="n">
@@ -51766,7 +51766,7 @@
       </c>
       <c r="AF469" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG469" t="n">
@@ -51878,7 +51878,7 @@
       </c>
       <c r="AF470" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG470" t="n">
@@ -51982,7 +51982,7 @@
       </c>
       <c r="AF471" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG471" t="n">
@@ -52094,7 +52094,7 @@
       </c>
       <c r="AF472" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG472" t="n">
@@ -52611,7 +52611,7 @@
       </c>
       <c r="AF477" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG477" t="n">
@@ -52728,7 +52728,7 @@
       </c>
       <c r="AF478" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG478" t="n">
@@ -52845,7 +52845,7 @@
       </c>
       <c r="AF479" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG479" t="n">
@@ -53364,7 +53364,7 @@
       </c>
       <c r="AF484" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG484" t="n">
@@ -53600,7 +53600,7 @@
       </c>
       <c r="AF486" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG486" t="n">
@@ -54283,7 +54283,7 @@
       </c>
       <c r="AF492" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG492" t="n">
@@ -54901,7 +54901,7 @@
       </c>
       <c r="AF498" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG498" t="n">
@@ -55005,7 +55005,7 @@
       </c>
       <c r="AF499" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG499" t="n">
@@ -55117,7 +55117,7 @@
       </c>
       <c r="AF500" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG500" t="n">
@@ -55229,7 +55229,7 @@
       </c>
       <c r="AF501" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG501" t="n">
@@ -55338,7 +55338,7 @@
       </c>
       <c r="AF502" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG502" t="n">
@@ -55577,7 +55577,7 @@
       </c>
       <c r="AF504" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG504" t="n">
@@ -55992,7 +55992,7 @@
       </c>
       <c r="AF508" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG508" t="n">
@@ -56342,7 +56342,7 @@
       </c>
       <c r="AF511" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG511" t="n">
@@ -56446,7 +56446,7 @@
       </c>
       <c r="AF512" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG512" t="n">
@@ -56550,7 +56550,7 @@
       </c>
       <c r="AF513" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG513" t="n">
@@ -56750,7 +56750,7 @@
       </c>
       <c r="AF515" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG515" t="n">
@@ -56958,7 +56958,7 @@
       </c>
       <c r="AF517" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG517" t="n">
@@ -57586,7 +57586,7 @@
       </c>
       <c r="AF523" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG523" t="n">
@@ -57695,7 +57695,7 @@
       </c>
       <c r="AF524" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG524" t="n">
@@ -58025,7 +58025,7 @@
       </c>
       <c r="AF527" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG527" t="n">
@@ -58347,7 +58347,7 @@
       </c>
       <c r="AF530" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG530" t="n">
@@ -58864,7 +58864,7 @@
       </c>
       <c r="AF535" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG535" t="n">
@@ -58973,7 +58973,7 @@
       </c>
       <c r="AF536" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG536" t="n">
@@ -59176,7 +59176,7 @@
       </c>
       <c r="AF538" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG538" t="n">
@@ -59381,7 +59381,7 @@
       </c>
       <c r="AF540" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG540" t="n">
@@ -60172,7 +60172,7 @@
       </c>
       <c r="AF547" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG547" t="n">
@@ -60377,7 +60377,7 @@
       </c>
       <c r="AF549" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG549" t="n">
@@ -60598,7 +60598,7 @@
       </c>
       <c r="AF551" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG551" t="n">
@@ -60821,7 +60821,7 @@
       </c>
       <c r="AF553" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG553" t="n">
@@ -61151,7 +61151,7 @@
       </c>
       <c r="AF556" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG556" t="n">
@@ -61805,7 +61805,7 @@
       </c>
       <c r="AF562" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG562" t="n">
@@ -61909,7 +61909,7 @@
       </c>
       <c r="AF563" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG563" t="n">
@@ -62264,7 +62264,7 @@
       </c>
       <c r="AF566" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG566" t="n">
@@ -62472,7 +62472,7 @@
       </c>
       <c r="AF568" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG568" t="n">
@@ -62685,7 +62685,7 @@
       </c>
       <c r="AF570" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG570" t="n">
@@ -63131,7 +63131,7 @@
       </c>
       <c r="AF574" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG574" t="n">
@@ -63331,7 +63331,7 @@
       </c>
       <c r="AF576" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG576" t="n">
@@ -63435,7 +63435,7 @@
       </c>
       <c r="AF577" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG577" t="n">
@@ -64633,7 +64633,7 @@
       </c>
       <c r="AF588" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG588" t="n">
@@ -65041,7 +65041,7 @@
       </c>
       <c r="AF592" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG592" t="n">
@@ -65365,7 +65365,7 @@
       </c>
       <c r="AF595" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG595" t="n">
@@ -65573,7 +65573,7 @@
       </c>
       <c r="AF597" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG597" t="n">
@@ -66581,7 +66581,7 @@
       </c>
       <c r="AF606" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG606" t="n">
@@ -66685,7 +66685,7 @@
       </c>
       <c r="AF607" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG607" t="n">
@@ -67554,7 +67554,7 @@
       </c>
       <c r="AF615" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG615" t="n">
@@ -67785,7 +67785,7 @@
       </c>
       <c r="AF617" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG617" t="n">
@@ -69367,7 +69367,7 @@
       </c>
       <c r="AF631" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG631" t="n">
@@ -69471,7 +69471,7 @@
       </c>
       <c r="AF632" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG632" t="n">
@@ -69775,7 +69775,7 @@
       </c>
       <c r="AF635" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG635" t="n">
@@ -69887,7 +69887,7 @@
       </c>
       <c r="AF636" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG636" t="n">
@@ -70312,7 +70312,7 @@
       </c>
       <c r="AF640" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG640" t="n">
@@ -70932,7 +70932,7 @@
       </c>
       <c r="AF646" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG646" t="n">
@@ -71502,7 +71502,7 @@
       </c>
       <c r="AF651" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG651" t="n">
@@ -71614,7 +71614,7 @@
       </c>
       <c r="AF652" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG652" t="n">
@@ -71842,7 +71842,7 @@
       </c>
       <c r="AF654" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG654" t="n">
@@ -72408,7 +72408,7 @@
       </c>
       <c r="AF659" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG659" t="n">
@@ -72891,7 +72891,7 @@
       </c>
       <c r="AF663" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG663" t="n">
@@ -73099,7 +73099,7 @@
       </c>
       <c r="AF665" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG665" t="n">
@@ -73545,7 +73545,7 @@
       </c>
       <c r="AF669" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG669" t="n">
@@ -74199,7 +74199,7 @@
       </c>
       <c r="AF675" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG675" t="n">
@@ -74417,7 +74417,7 @@
       </c>
       <c r="AF677" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG677" t="n">
@@ -75166,7 +75166,7 @@
       </c>
       <c r="AF684" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG684" t="n">
@@ -75366,7 +75366,7 @@
       </c>
       <c r="AF686" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG686" t="n">
@@ -75470,7 +75470,7 @@
       </c>
       <c r="AF687" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG687" t="n">
@@ -76228,7 +76228,7 @@
       </c>
       <c r="AF694" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG694" t="n">
@@ -76444,7 +76444,7 @@
       </c>
       <c r="AF696" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG696" t="n">
@@ -77762,7 +77762,7 @@
       </c>
       <c r="AF708" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG708" t="n">
@@ -78076,7 +78076,7 @@
       </c>
       <c r="AF711" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG711" t="n">
@@ -78180,7 +78180,7 @@
       </c>
       <c r="AF712" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG712" t="n">
@@ -78411,7 +78411,7 @@
       </c>
       <c r="AF714" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG714" t="n">
@@ -78523,7 +78523,7 @@
       </c>
       <c r="AF715" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG715" t="n">
@@ -78850,7 +78850,7 @@
       </c>
       <c r="AF718" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG718" t="n">
@@ -78967,7 +78967,7 @@
       </c>
       <c r="AF719" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG719" t="n">
@@ -79071,7 +79071,7 @@
       </c>
       <c r="AF720" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG720" t="n">
@@ -79183,7 +79183,7 @@
       </c>
       <c r="AF721" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG721" t="n">
@@ -79287,7 +79287,7 @@
       </c>
       <c r="AF722" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG722" t="n">
@@ -79487,7 +79487,7 @@
       </c>
       <c r="AF724" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG724" t="n">
@@ -79827,7 +79827,7 @@
       </c>
       <c r="AF727" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG727" t="n">
@@ -80146,7 +80146,7 @@
       </c>
       <c r="AF730" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG730" t="n">
@@ -80250,7 +80250,7 @@
       </c>
       <c r="AF731" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG731" t="n">
@@ -80929,7 +80929,7 @@
       </c>
       <c r="AF737" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG737" t="n">
@@ -81147,7 +81147,7 @@
       </c>
       <c r="AF739" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG739" t="n">
@@ -81251,7 +81251,7 @@
       </c>
       <c r="AF740" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG740" t="n">
@@ -81770,7 +81770,7 @@
       </c>
       <c r="AF745" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG745" t="n">
@@ -82759,7 +82759,7 @@
       </c>
       <c r="AF754" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG754" t="n">
@@ -82868,7 +82868,7 @@
       </c>
       <c r="AF755" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG755" t="n">
@@ -83289,7 +83289,7 @@
       </c>
       <c r="AF759" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG759" t="n">
@@ -84146,7 +84146,7 @@
       </c>
       <c r="AF767" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG767" t="n">
@@ -84349,7 +84349,7 @@
       </c>
       <c r="AF769" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG769" t="n">
@@ -84458,7 +84458,7 @@
       </c>
       <c r="AF770" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG770" t="n">
@@ -85071,7 +85071,7 @@
       </c>
       <c r="AF776" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG776" t="n">
@@ -85408,7 +85408,7 @@
       </c>
       <c r="AF779" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG779" t="n">
@@ -85525,7 +85525,7 @@
       </c>
       <c r="AF780" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG780" t="n">
@@ -85857,7 +85857,7 @@
       </c>
       <c r="AF783" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG783" t="n">
@@ -85966,7 +85966,7 @@
       </c>
       <c r="AF784" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG784" t="n">
@@ -86078,7 +86078,7 @@
       </c>
       <c r="AF785" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG785" t="n">
